--- a/Capitulo000_ClaseOnline/Cohorte06/Clase24_03062026/EsquemaDiagramaCompleto.xlsx
+++ b/Capitulo000_ClaseOnline/Cohorte06/Clase24_03062026/EsquemaDiagramaCompleto.xlsx
@@ -136,15 +136,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>82823</xdr:colOff>
+      <xdr:colOff>14788</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>129625</xdr:rowOff>
+      <xdr:rowOff>75196</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>267111</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>43900</xdr:rowOff>
+      <xdr:colOff>199076</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>179971</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -159,8 +159,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6824866" y="1272625"/>
-          <a:ext cx="2635941" cy="676275"/>
+          <a:off x="6750324" y="1218196"/>
+          <a:ext cx="2633573" cy="676275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -343,13 +343,8 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr lang="en-US" sz="2000"/>
-            <a:t>MONGO</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000" baseline="0"/>
-            <a:t> DB</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="2000"/>
+            <a:t>cliente</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1231,16 +1226,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>133349</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>200024</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>228598</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>42182</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>295274</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>4082</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1249,8 +1244,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6229349" y="4695825"/>
-          <a:ext cx="4943475" cy="914400"/>
+          <a:off x="6964134" y="4804682"/>
+          <a:ext cx="4965247" cy="914400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1312,15 +1307,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>545408</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>138319</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>240609</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>90694</xdr:rowOff>
+      <xdr:colOff>205230</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>83891</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>512753</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>36266</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1329,8 +1324,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13416582" y="5091319"/>
-          <a:ext cx="2146853" cy="523875"/>
+          <a:off x="13063980" y="2179391"/>
+          <a:ext cx="2144487" cy="523875"/>
         </a:xfrm>
         <a:prstGeom prst="ellipse">
           <a:avLst/>
@@ -1357,8 +1352,13 @@
           <a:pPr algn="l"/>
           <a:r>
             <a:rPr lang="en-US" sz="1100"/>
-            <a:t>VectorContribuyentes</a:t>
-          </a:r>
+            <a:t>POSTGRE</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> - SQL</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -1597,137 +1597,6 @@
             <a:t> =&gt; ELIMINAR DATOS</a:t>
           </a:r>
           <a:endParaRPr lang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>107673</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>603388</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>107673</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="Cilindro 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15090913" y="488673"/>
-          <a:ext cx="2061127" cy="2095500"/>
-        </a:xfrm>
-        <a:prstGeom prst="can">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent4">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent4"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent4"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000"/>
-            <a:t>MONGO</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000" baseline="0"/>
-            <a:t> DB</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="2000"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>82826</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>421585</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="Nube 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11728174" y="0"/>
-          <a:ext cx="2177498" cy="1962150"/>
-        </a:xfrm>
-        <a:prstGeom prst="cloud">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="2000"/>
-            <a:t>INTERNET</a:t>
-          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
